--- a/data/df_extraccion_datos/df_modelos_celulares.xlsx
+++ b/data/df_extraccion_datos/df_modelos_celulares.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:D221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,88 +449,38 @@
           <t>Modelo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Con micrófono</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Con micrófono desmontable</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Con micrófono flexible</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Formato del auricular</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Es inalámbrico</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Con Bluetooth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18612467</t>
+          <t>17415926</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81.999</t>
+          <t>34.999</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11 Lite 5G NE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Negro trufa</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>A12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18492029</t>
+          <t>17493810</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>134.999</t>
+          <t>65.999</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -540,244 +490,151 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Z Flip3 5G</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Phantom black</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>A52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>869775762</t>
+          <t>18730239</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.350</t>
+          <t>112.999</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Haiyu</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B16</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>S21 FE 5G</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>921491657</t>
+          <t>18612467</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.790</t>
+          <t>81.999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P&amp;S Mobile</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NeoPro</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>11 Lite 5G NE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18568496</t>
+          <t>18329757</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>104.999</t>
+          <t>43.999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11T</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Gris meteorito</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>A22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16244155</t>
+          <t>18495452</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.992</t>
+          <t>69.999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10T 5G</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Negro cósmico</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>20 Lite</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1111289458</t>
+          <t>18576330</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13.999</t>
+          <t>21.999</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>YOLO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>E20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16951113</t>
+          <t>18192280</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>42.655</t>
+          <t>40.593</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>K52 (48 Mpx)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>M12 (5000 mAh)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1126526347</t>
+          <t>18492029</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20.999</t>
+          <t>134.999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -787,30 +644,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A03 Core</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Z Flip3 5G</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1128670918</t>
+          <t>17343137</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>97.699</t>
+          <t>174.999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -820,96 +666,63 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A52s 5G</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>S21+ 5G</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>795098537</t>
+          <t>18574687</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>79.999</t>
+          <t>101.799</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>iPhone 7</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>20 Pro</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>805110436</t>
+          <t>18967702</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39.999</t>
+          <t>229.999</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>G6 Single SIM</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>S22 Ultra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1102514360</t>
+          <t>17343021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>44.999</t>
+          <t>214.999</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -919,117 +732,4553 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A22</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>S21 Ultra 5G</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1118532788</t>
+          <t>17331535</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.990</t>
+          <t>149.999</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>106 (2018)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>S21 5G</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1126892862</t>
+          <t>17953707</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>38.999</t>
+          <t>81.999</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Note 10 Pro (Global)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>912489012</t>
+          <t>18568496</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>104.999</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>11T</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17798685</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>92.149</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Poco X3 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17356625</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14.797</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>L1 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18577244</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>82.999</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A52s 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>18967705</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>149.999</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15587265</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6.790</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>106 (2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12984750</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4.579</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sansei</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>S191</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18115577</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13.989</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>YOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15591334</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>153.284</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>iPhone SE (2nd Generation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>17448928</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17.999</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>L7+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>17324469</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>59.999</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Poco M3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>18375406</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>29.999</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15927746</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>28.299</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>18597567</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>32.999</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>17917185</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>15.555</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>UP32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16163653</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>229.602</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>iPhone 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>18500844</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>258.771</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>iPhone 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16211370</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>97.900</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>S20 FE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>18303899</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>26.999</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3H</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>18967709</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>189.999</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>S22+</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>18514380</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>259.999</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Z Fold3 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>18604772</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>14.499</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>A3 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16054769</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>6.149</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1115854443</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>119.999</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1124526343</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>99.999</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moto G200</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>18447112</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>28.299</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>9AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16163952</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>79.049</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Poco X3 NFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>15810332</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4.999</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Energizer</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>E10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>18413943</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>27.519</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>18027046</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>74.399</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Note 10S</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9919978</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>9.299</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Philco</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>P241</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>15149568</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>179.999</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>iPhone 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16372311</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>58.999</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>XCover Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16069874</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>34.999</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16229386</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>59.990</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Armor X5 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>18514724</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>247.424</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>iPhone 13 mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>13221277</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>13.900</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>17459959</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>69.499</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Note 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>18494248</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>334.850</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>iPhone 13 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>17875205</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>94.199</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Poco F3 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>18494236</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>475.237</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>iPhone 13 Pro Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1104368087</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>52.999</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>G60s</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12866685</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>219.990</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>iPhone XR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>18107542</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6.999</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Panacom</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MP-1112</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>18374104</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>14.499</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>17327327</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>38.299</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>10 SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>18922850</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>37.799</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>V30 Vita</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>17798691</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>38.300</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>E7i Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1122193035</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>31.999</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TCL 20B Space Gray</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14906505</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>79.000</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>9T</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>18904853</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>20.999</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>A03 Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16203315</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>70.900</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>S42 Dual SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>18010643</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>38.454</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16179752</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>12.634</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Noblex</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>N405</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16241590</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>181.000</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>S62 Pro Dual SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16999810</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21.900</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>A5 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>6148402</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7.000</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>B220</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1124422519</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>22.999</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>A03 Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>18708200</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>57.599</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>20 SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16244155</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>112.992</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>10T 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>15949974</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>59.999</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>9 (Global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>15794532</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20.989</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1V (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>17409255</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>18.664</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>A3 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>18061593</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>73.999</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Poco M3 Pro 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>18416364</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7.490</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>110 (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16163664</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>249.999</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>iPhone 12 mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16163695</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>419.999</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>iPhone 12 Pro Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>15698682</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>43.000</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>15711867</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>15.999</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Quantum</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>UP32</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>18465085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>34.700</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>20 E</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>15534164</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>92.900</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Armor 7 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1126722048</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>24.350</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>A03 Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>901991696</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>15.900</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>17086599</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>80.900</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Blackview</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BV6300 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10861644</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>194.500</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>S61 Dual SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>13141507</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>29.699</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>E5 Play (Go Edition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>795491376</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>64.999</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>iPhone 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>18385213</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>86.499</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Poco X3 GT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>15188554</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>64.900</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Note 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>15960760</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>74.999</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>A21s</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>869775762</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5.350</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Haiyu</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>921491657</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>23.790</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>P&amp;S Mobile</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NeoPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>17356051</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>28.399</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>L10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>8928199</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>32.999</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>5 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>15793963</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>89.990</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Note 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>18915991</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>12.800</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>E1272</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>18606485</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>54.123</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>G20</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>14186099</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>79.999</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>S10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16163686</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>359.990</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>iPhone 12 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16107499</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>31.999</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>A01 Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>17918024</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>103.400</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>11 Lite 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>15239257</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>99.990</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Note 8 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>17966485</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>63.470</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Note 10 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>17850379</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>26.999</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>L10 Lite</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>15485764</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>7.499</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>105 (2017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>17463748</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>63.725</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Note 9T</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1116998525</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>16.999</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>15098621</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>8.717</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9456317</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5.500</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BLU</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>15290674</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>135.900</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Blackview</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BV9800 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1116959576</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>17.999</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>17918017</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>99.869</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>11 Lite</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>899435794</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>23.999</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16020327</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7.900</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>17451157</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>22.499</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>15713173</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>25.099</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>L9S</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>6250947</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>6.599</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>D245</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>790282792</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>59.999</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>S8+</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>18576545</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>31.189</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>A71</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>8752452</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>129.360</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>iPhone 8 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1126048282</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>24.999</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>A03 Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>18726250</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>49.000</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>G31</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>15977276</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>119.000</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Note 10 Lite</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>18529712</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>69.327</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>15534754</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>72.900</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Armor X5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>15485730</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>6.990</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>106 (2018) Dual SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>916552657</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>4.899</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>A6 Mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>738032215</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>42.999</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1114799671</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>6.998</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>BLU - IPRO - NOKIA - GENERICO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>A20 - JOY - 110 - 210 - 106 BLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>6240138</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>98.000</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>iPhone 7 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>16160393</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>259.999</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Z Fold2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>805110436</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>39.999</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>G6 Single SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>18528783</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>49.009</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>A03s</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1110012802</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>84.999</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>934228008</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>59.999</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>A51</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>15150713</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>242.211</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>iPhone 11 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>759206170</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>21.999</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>J7 Prime</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>928610337</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>35.999</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>5H</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>804738934</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>49.999</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>925663449</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>18.400</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>931498757</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>25.799</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>L7+</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>15811795</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>79.999</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Note 9 Pro (64 Mpx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>17706115</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>74.089</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>839623915</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>39.999</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Z Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>16947957</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>85.038</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>10T Lite 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>15970241</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>101.900</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>10 Lite</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>16006169</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>15.498</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>8752431</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>98.000</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>iPhone 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>18325189</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>75.669</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>8 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>17464698</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>38.001</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>14548566</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5.500</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>BLU</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Z5</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>919321247</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>74.999</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>A52</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>14071404</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Kanji</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Fon</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1114578320</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>6.948</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>T-36</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>12598993</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>50.000</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1123517465</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>47.999</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Note8</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>16180693</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>15.099</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>L1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>884200895</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>8.550</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BLU</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Jenny TV 2.8 Dual Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1111781789</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>142.500</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Doogee</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>S96 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>918523766</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>7.350</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Luo</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>843530851</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>39.999</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>A30 Duos</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1117089601</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>54.999</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>A70</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1117136529</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>95.999</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Z Flip</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1117136530</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>39.999</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>A50</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1123523835</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>75.999</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Note10</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>685089328</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>7.989</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Panacom</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>MP-1112</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1123529460</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>48.999</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>S9 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1106321051</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>169.899</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>A71</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1119701935</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>44.999</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>iPhone 6s</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1113990242</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>7.999</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>210 Dual SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>631735527</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>19.999</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>P9 Lite</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>900567945</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>8.100</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>756020415</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>21.999</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>14112943</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7.500</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1101802024</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>99.999</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>S20+</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>925424859</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>149.899</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>G30</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>805396921</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>39.999</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Z3 Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1106291893</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>49.889</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>925626262</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>229.899</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Edge Special Edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>915876881</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>40.999</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>S9 Duos</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>7979519</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>195.900</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>iPhone X</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>935637461</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>6.799</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Open II</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>15145876</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Note10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>923944482</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>23.999</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>S7 Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>926755388</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5.450</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Logic</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>909521542</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>8.999</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Philco</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>P241</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1115631556</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>169.899</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>One Fusion Dual SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>935720655</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>139.899</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Velvet</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>843646861</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>39.999</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>A10 Duos</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1107875637</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>60.000</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>iPhone 5s</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>925623838</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>169.899</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>G9 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1106226809</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>39.999</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>A10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>15182041</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>50.000</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>One Zoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1121438716</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>195.000</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>iPhone XS Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>885832552</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>9.098</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Kanji</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Müv</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>17770116</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>G30 Dual SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>902533895</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>19.999</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1112810785</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>46.000</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>K22+</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>735174061</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>80.375</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1128639208</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>26.499</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>G7 Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1104872713</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>23.999</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>J7 (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>923941702</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>18.999</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1124742259</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>15.000</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>LG K4 8 GB índigo 1 GB RAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1110823363</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>29.999</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>XA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1129934797</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>45.999</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1122647164</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>14.999</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>J111M</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>925619850</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>169.899</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>G9 Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1126952728</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>43.999</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>S8+ Duos</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>787102694</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>29.999</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>iPhone SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1124754833</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>15.999</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>J2 Prime</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>929961718</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>19.999</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>BlackBerry</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>9810</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1125855165</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>79.999</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>G100</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1108656835</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>34.999</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>A30</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1116905394</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>28.999</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>E6i</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>925624320</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>398.999</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>P30 Pro Dual SIM</t>
         </is>
       </c>
     </row>
